--- a/results/Int Task Remove ACC -0.1/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7719671390210832</v>
+        <v>0.768332273899498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.774432437527644</v>
+        <v>0.7694421416193145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7748179425392092</v>
+        <v>0.7816129819719004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7800455838527782</v>
+        <v>0.7796134315263339</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7804310888643433</v>
+        <v>0.7780926807220907</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7804310888643433</v>
+        <v>0.7769361656873953</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7800455838527782</v>
+        <v>0.7697089739282599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7669891696052864</v>
+        <v>0.7722888363065961</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7668663880718223</v>
+        <v>0.7689633419779911</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7758811629441464</v>
+        <v>0.7704799839513901</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7733987040264125</v>
+        <v>0.766815631926099</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7733987040264125</v>
+        <v>0.7508151195307231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7809647534822342</v>
+        <v>0.749925436804973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7797615911326596</v>
+        <v>0.7713696666771401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7783636218618804</v>
+        <v>0.7641088791834545</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7802150127011213</v>
+        <v>0.7684427289404292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7762371810520057</v>
+        <v>0.7671929192759757</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7786812103165491</v>
+        <v>0.758521110931182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7786812103165491</v>
+        <v>0.7718230882456018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7531020464394564</v>
+        <v>0.7766398464747439</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7545212849522529</v>
+        <v>0.7753392806645671</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7545212849522529</v>
+        <v>0.7826213374002702</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7567410203918857</v>
+        <v>0.7859427228980309</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7932576502804881</v>
+        <v>0.7887173921975719</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8248854965522076</v>
+        <v>0.7923097188351222</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.825368405024375</v>
+        <v>0.7855825959593274</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8210091771945387</v>
+        <v>0.7474698061356929</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8165779239769615</v>
+        <v>0.7517864954814946</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8277109219974719</v>
+        <v>0.7517864954814946</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8342857764360968</v>
+        <v>0.6281150375958022</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8362853268816632</v>
+        <v>0.6344607642908762</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8191324082824362</v>
+        <v>0.6217775285624167</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7948373748921431</v>
+        <v>0.6367017689725264</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7956124937461178</v>
+        <v>0.6147581953048149</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7974679934162028</v>
+        <v>0.6084165774405851</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7729747693616569</v>
+        <v>0.6165924257328825</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7489794389270634</v>
+        <v>0.6423190241285048</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.750428164343566</v>
+        <v>0.6440181465305758</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7514063077804338</v>
+        <v>0.6702530314712274</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7743664545382036</v>
+        <v>0.669528668762976</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.765449083126482</v>
+        <v>0.6701556280106249</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7171422839782183</v>
+        <v>0.6901504073784934</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7177143782492996</v>
+        <v>0.6808180440515006</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7110716072537784</v>
+        <v>0.6776112224255153</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7236279526179294</v>
+        <v>0.7049347058439659</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7217470748749828</v>
+        <v>0.7082814694145882</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6605622330770551</v>
+        <v>0.701854774582289</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6544408002068918</v>
+        <v>0.6987199783440445</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.609150124594253</v>
+        <v>0.695707963639264</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.609150124594253</v>
+        <v>0.7222899239382903</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5765228656436483</v>
+        <v>0.7289409125955001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5880406435879277</v>
+        <v>0.7285595164147792</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5915142975228583</v>
+        <v>0.7306057141752247</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6628073465895495</v>
+        <v>0.7322705157549493</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6427610859881617</v>
+        <v>0.7317155818950412</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5649734255322749</v>
+        <v>0.7326306426936529</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5663713948030541</v>
+        <v>0.7326306426936529</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5663713948030541</v>
+        <v>0.7333296273290424</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5637236158678214</v>
+        <v>0.706512980280029</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5634862704625818</v>
+        <v>0.6656240709812613</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5391315381770809</v>
+        <v>0.6768593063810143</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5392289416376833</v>
+        <v>0.7427915396755957</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5395424212615078</v>
+        <v>0.7641163717573469</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5657060059022146</v>
+        <v>0.7688062396221809</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5575555356827789</v>
+        <v>0.8046821335950094</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5687687767527185</v>
+        <v>0.7964760733112102</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5699211829565697</v>
+        <v>0.7885752749895466</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5699211829565697</v>
+        <v>0.7889607800011118</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5723569945594246</v>
+        <v>0.7835637098391997</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5769364073833274</v>
+        <v>0.7835637098391997</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5179877363484096</v>
+        <v>0.7733670418593184</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4933806735098841</v>
+        <v>0.7679233243825273</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5373673995692978</v>
+        <v>0.7358091858955922</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5557097038499745</v>
+        <v>0.6787928738371405</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5477663670442763</v>
+        <v>0.6951665647515486</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5535399994682689</v>
+        <v>0.6964328097393793</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5336680016338645</v>
+        <v>0.6964328097393793</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5348965420563007</v>
+        <v>0.6533522017290927</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.534795029764854</v>
+        <v>0.5975542788639324</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5488467478603867</v>
+        <v>0.5951259598349701</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5488467478603867</v>
+        <v>0.6050180909405114</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5085113222459353</v>
+        <v>0.6050180909405114</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5016909047403824</v>
+        <v>0.6037470120340405</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5021484351396882</v>
+        <v>0.5703830638826518</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4925574571654385</v>
+        <v>0.5703830638826518</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4792136664547799</v>
+        <v>0.5716500339582784</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4778328575951739</v>
+        <v>0.5215273732727805</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4979037711816273</v>
+        <v>0.5210444648006129</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.499034908143461</v>
+        <v>0.5039464111779535</v>
       </c>
     </row>
   </sheetData>
